--- a/backend/static_assets/Print_Speed_Scenarios.xlsx
+++ b/backend/static_assets/Print_Speed_Scenarios.xlsx
@@ -12,20 +12,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B. Single 160 @485, no setup" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C. By finish 190-135 @485, no s" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D. By finish 190-135 @485 +10mi" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="E. By finish 220-160 @485 +5min" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F. iQuote 144-102 @319 +10min" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G. iQuote 144-102 @319 +7min" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H. iQuote 144-102 @319 +5min" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F. iQuote 144-102 @319 +10min" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G. iQuote 144-102 @319 +7min" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H. G + 2-sided as full 2nd pass" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="I. H + ink coverage tiers" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A. Today 75-75 @485, no setup'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B. Single 160 @485, no setup'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C. By finish 190-135 @485, no s'!$A$1:$H$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D. By finish 190-135 @485 +10mi'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'E. By finish 220-160 @485 +5min'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'F. iQuote 144-102 @319 +10min'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'G. iQuote 144-102 @319 +7min'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'H. iQuote 144-102 @319 +5min'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'F. iQuote 144-102 @319 +10min'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'G. iQuote 144-102 @319 +7min'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'H. G + 2-sided as full 2nd pass'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'I. H + ink coverage tiers'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,8 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,55 +498,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>2-sided</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Ink</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Δ % all rows</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAPE % all</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Δ% 1-49</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Δ% 50-199</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Δ% 200-999</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Δ% 1000-4999</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Δ% 5000+</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Δ% Satin</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Δ% Gloss</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Rows within ±20%</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Rows</t>
         </is>
@@ -568,38 +580,48 @@
       <c r="E2" t="n">
         <v>485</v>
       </c>
-      <c r="F2" t="n">
-        <v>82</v>
-      </c>
-      <c r="G2" t="n">
-        <v>53.5</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H2" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.1</v>
       </c>
-      <c r="I2" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>77.2</v>
-      </c>
       <c r="K2" t="n">
-        <v>123.8</v>
+        <v>45.4</v>
       </c>
       <c r="L2" t="n">
-        <v>60.1</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>103.6</v>
+        <v>63.5</v>
       </c>
       <c r="N2" t="n">
-        <v>49.3</v>
+        <v>45.3</v>
       </c>
       <c r="O2" t="n">
-        <v>153</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>430</v>
+        <v>48.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>152</v>
+      </c>
+      <c r="R2" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="3">
@@ -620,38 +642,48 @@
       <c r="E3" t="n">
         <v>485</v>
       </c>
-      <c r="F3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>31.2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>-40.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="K3" t="n">
-        <v>29.7</v>
+        <v>-11.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.5</v>
+        <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>20.7</v>
+        <v>-2.7</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.6</v>
+        <v>-13.8</v>
       </c>
       <c r="O3" t="n">
-        <v>162</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>430</v>
+        <v>-9.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>158</v>
+      </c>
+      <c r="R3" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="4">
@@ -672,38 +704,48 @@
       <c r="E4" t="n">
         <v>485</v>
       </c>
-      <c r="F4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>30.3</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H4" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J4" t="n">
         <v>-38.7</v>
       </c>
-      <c r="I4" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9.6</v>
-      </c>
       <c r="K4" t="n">
-        <v>19.8</v>
+        <v>-11.1</v>
       </c>
       <c r="L4" t="n">
-        <v>-13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>9.199999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9</v>
+        <v>-22</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>-5.9</v>
       </c>
       <c r="P4" t="n">
-        <v>430</v>
+        <v>0.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>162</v>
+      </c>
+      <c r="R4" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="5">
@@ -724,96 +766,116 @@
       <c r="E5" t="n">
         <v>485</v>
       </c>
-      <c r="F5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40.9</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>56.8</v>
       </c>
-      <c r="I5" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23.1</v>
-      </c>
       <c r="K5" t="n">
-        <v>26.8</v>
+        <v>24.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-11.2</v>
+        <v>21.9</v>
       </c>
       <c r="M5" t="n">
-        <v>22.1</v>
+        <v>-1.5</v>
       </c>
       <c r="N5" t="n">
-        <v>20.7</v>
+        <v>-20</v>
       </c>
       <c r="O5" t="n">
-        <v>148</v>
+        <v>7.4</v>
       </c>
       <c r="P5" t="n">
-        <v>430</v>
+        <v>20.4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>145</v>
+      </c>
+      <c r="R5" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. By finish 220-160 @485 +5min</t>
+          <t>F. iQuote 144-102 @319 +10min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="C6" t="n">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>485</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>19</v>
+        <v>319</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>21.2</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2</v>
+        <v>19.2</v>
       </c>
       <c r="K6" t="n">
-        <v>13.1</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>-18.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>7.2</v>
+        <v>-10.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>-26.5</v>
       </c>
       <c r="O6" t="n">
-        <v>293</v>
+        <v>-3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>430</v>
+        <v>5.7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>239</v>
+      </c>
+      <c r="R6" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. iQuote 144-102 @319 +10min</t>
+          <t>G. iQuote 144-102 @319 +7min</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -823,49 +885,59 @@
         <v>102</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>319</v>
       </c>
-      <c r="F7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="G7" t="n">
-        <v>23.4</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>19.2</v>
+        <v>-3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>16.6</v>
       </c>
       <c r="J7" t="n">
-        <v>10.4</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>14.7</v>
+        <v>-1.2</v>
       </c>
       <c r="L7" t="n">
-        <v>-18.3</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>9.5</v>
+        <v>-12.2</v>
       </c>
       <c r="N7" t="n">
-        <v>6.1</v>
+        <v>-26.9</v>
       </c>
       <c r="O7" t="n">
-        <v>244</v>
+        <v>-6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>430</v>
+        <v>1.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>294</v>
+      </c>
+      <c r="R7" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. iQuote 144-102 @319 +7min</t>
+          <t>H. G + 2-sided as full 2nd pass</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -880,44 +952,54 @@
       <c r="E8" t="n">
         <v>319</v>
       </c>
-      <c r="F8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>18.9</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>full 2nd pass</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>flat $0.05</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>0.3</v>
+        <v>-1.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6</v>
+        <v>16.7</v>
       </c>
       <c r="J8" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>13.4</v>
+        <v>2.1</v>
       </c>
       <c r="L8" t="n">
-        <v>-18.8</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>-11.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.2</v>
+        <v>-25.6</v>
       </c>
       <c r="O8" t="n">
-        <v>299</v>
+        <v>-5.8</v>
       </c>
       <c r="P8" t="n">
-        <v>430</v>
+        <v>3.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>292</v>
+      </c>
+      <c r="R8" t="n">
+        <v>419</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. iQuote 144-102 @319 +5min</t>
+          <t>I. H + ink coverage tiers</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -927,43 +1009,53 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>319</v>
       </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>20.6</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>full 2nd pass</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>coverage tiers</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>-12.2</v>
+        <v>-4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.3</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>12.5</v>
+        <v>-3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.1</v>
+        <v>-0.7</v>
       </c>
       <c r="M9" t="n">
-        <v>5.3</v>
+        <v>-11.3</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4</v>
+        <v>-11.4</v>
       </c>
       <c r="O9" t="n">
-        <v>282</v>
+        <v>-6.7</v>
       </c>
       <c r="P9" t="n">
-        <v>430</v>
+        <v>-2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>360</v>
+      </c>
+      <c r="R9" t="n">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -1067,25 +1159,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>35656.5</v>
+        <v>35342.66</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>44.7</v>
+        <v>45.4</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1095,22 +1187,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>195796.14</v>
+        <v>186441.44</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>77.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>57.8</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>67.7</v>
+        <v>66.3</v>
       </c>
       <c r="H4" t="n">
         <v>32</v>
@@ -1123,22 +1215,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>142596.42</v>
+        <v>95231.28999999999</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>123.8</v>
+        <v>63.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>45.9</v>
+        <v>45.2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -1151,22 +1243,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>41704.74</v>
+        <v>36773.07</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>60.1</v>
+        <v>45.3</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>125.1</v>
+        <v>34.1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1175,36 +1267,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>285324.56</v>
+        <v>229588.67</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>103.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>138527.54</v>
+        <v>132298.11</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>49.3</v>
+        <v>48.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.1</v>
+        <v>38.9</v>
       </c>
     </row>
   </sheetData>
@@ -1309,22 +1401,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21771.92</v>
+        <v>21578.32</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-11.7</v>
+        <v>-11.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-20.5</v>
+        <v>-19.9</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>26.8</v>
+        <v>26.5</v>
       </c>
       <c r="H3" t="n">
         <v>39</v>
@@ -1337,25 +1429,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>119975.12</v>
+        <v>114289.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-2.8</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="H4" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -1365,22 +1457,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>82609.92</v>
+        <v>56674.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>29.7</v>
+        <v>-2.7</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-10</v>
+        <v>-10.6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35.5</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
         <v>29</v>
@@ -1393,22 +1485,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>24877.38</v>
+        <v>21835.2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-4.5</v>
+        <v>-13.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-10.5</v>
+        <v>-10.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1417,36 +1509,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>169191.67</v>
+        <v>138098.03</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20.7</v>
+        <v>3.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>32.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>84842.28999999999</v>
+        <v>81079.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-8.6</v>
+        <v>-9.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
     </row>
   </sheetData>
@@ -1551,22 +1643,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>21782.88</v>
+        <v>21606.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-11.6</v>
+        <v>-11.1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-16.1</v>
+        <v>-15.9</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="H3" t="n">
         <v>46</v>
@@ -1579,25 +1671,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>121061.26</v>
+        <v>115252.37</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-4.4</v>
+        <v>-4.8</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="H4" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -1607,22 +1699,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>76336.96000000001</v>
+        <v>53275.26</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>19.8</v>
+        <v>-8.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-16.3</v>
+        <v>-17.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>36.1</v>
+        <v>22.5</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -1635,22 +1727,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22533.01</v>
+        <v>19754.07</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-13.5</v>
+        <v>-22</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-19.1</v>
+        <v>-19.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1659,36 +1751,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>153012.17</v>
+        <v>125351.65</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>-5.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>32.9</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>93614.39</v>
+        <v>89448.53999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
     </row>
   </sheetData>
@@ -1793,25 +1885,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>30609.88</v>
+        <v>30271.38</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>37</v>
+        <v>37.4</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -1821,25 +1913,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>135999.26</v>
+        <v>129867.04</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="H4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -1849,22 +1941,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>80766.62</v>
+        <v>57381.6</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>26.8</v>
+        <v>-1.5</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>35.9</v>
+        <v>20.2</v>
       </c>
       <c r="H5" t="n">
         <v>33</v>
@@ -1877,22 +1969,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>23115.01</v>
+        <v>20255.23</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-11.2</v>
+        <v>-20</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-18.1</v>
+        <v>-18.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>70.5</v>
+        <v>25.7</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -1901,36 +1993,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>171054.17</v>
+        <v>142989.48</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>22.1</v>
+        <v>7.4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>40.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>111995.89</v>
+        <v>107345.04</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
     </row>
   </sheetData>
@@ -2010,22 +2102,22 @@
         <v>91</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8284.26</v>
+        <v>9547.75</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8011.59</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3.4</v>
+        <v>19.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.2</v>
+        <v>23.2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>23.4</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -2035,25 +2127,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>24390.64</v>
+        <v>25714.83</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-1</v>
+        <v>5.8</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1</v>
+        <v>10.6</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14.2</v>
+        <v>18.4</v>
       </c>
       <c r="H3" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -2063,25 +2155,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>118459</v>
+        <v>116426.16</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.1</v>
+        <v>3.8</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="H4" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
@@ -2091,25 +2183,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>72046.38</v>
+        <v>51947.63</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>13.1</v>
+        <v>-10.8</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-14.2</v>
+        <v>-11.9</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33.4</v>
+        <v>19.9</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2119,22 +2211,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>21119.02</v>
+        <v>18616.82</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-18.9</v>
+        <v>-26.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-24.8</v>
+        <v>-24.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2143,36 +2235,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>150266.26</v>
+        <v>127968.35</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7.2</v>
+        <v>-3.9</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>94033.03999999999</v>
+        <v>94284.84</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17.2</v>
+        <v>21.8</v>
       </c>
     </row>
   </sheetData>
@@ -2252,22 +2344,22 @@
         <v>91</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9547.75</v>
+        <v>8038.88</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8011.59</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>19.2</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>23.4</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -2277,25 +2369,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>25986.2</v>
+        <v>24004.99</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>5.4</v>
+        <v>-1.2</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10.3</v>
+        <v>-0.2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>18.4</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -2305,25 +2397,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>122009.47</v>
+        <v>113542.4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>10.4</v>
+        <v>6.6</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="H4" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
@@ -2333,25 +2425,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>73103.78</v>
+        <v>51137.37</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>14.7</v>
+        <v>-12.2</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-8.6</v>
+        <v>-14.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33</v>
+        <v>21.2</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2361,22 +2453,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>21263.39</v>
+        <v>18517.93</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-18.3</v>
+        <v>-26.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-24.5</v>
+        <v>-24.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>71.2</v>
+        <v>33.6</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2385,36 +2477,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>153474.86</v>
+        <v>124488.06</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>24.7</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>98435.72</v>
+        <v>90753.50999999999</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>
@@ -2494,22 +2586,22 @@
         <v>91</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8038.88</v>
+        <v>8268.610000000001</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8011.59</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -2519,25 +2611,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>24244.46</v>
+        <v>24820.02</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-1.6</v>
+        <v>2.1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-0.8</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -2547,25 +2639,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>119061.91</v>
+        <v>114517.78</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="H4" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5">
@@ -2575,22 +2667,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>72229.72</v>
+        <v>51652.84</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>13.4</v>
+        <v>-11.3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-14.4</v>
+        <v>-14.8</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>33.8</v>
+        <v>20.7</v>
       </c>
       <c r="H5" t="n">
         <v>23</v>
@@ -2603,22 +2695,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>21148.55</v>
+        <v>18843.82</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-18.8</v>
+        <v>-25.6</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-24.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>71.7</v>
+        <v>28.2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2627,36 +2719,36 @@
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>149914.82</v>
+        <v>125527.08</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7</v>
+        <v>-5.8</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>20.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>94808.69</v>
+        <v>92576</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>
@@ -2736,22 +2828,22 @@
         <v>91</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7032.97</v>
+        <v>8175.49</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>8011.59</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-12.2</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>-12.2</v>
+        <v>2.7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.2</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -2761,25 +2853,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>23083.3</v>
+        <v>23362.63</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24645.23</v>
+        <v>24306.63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-6.3</v>
+        <v>-3.9</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>16.3</v>
+        <v>9.5</v>
       </c>
       <c r="H3" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -2789,25 +2881,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>117096.87</v>
+        <v>105803.79</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>110504.71</v>
+        <v>106499.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>6</v>
+        <v>-0.7</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-3</v>
+        <v>-0.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21.6</v>
+        <v>12.3</v>
       </c>
       <c r="H4" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
@@ -2817,25 +2909,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>71647.00999999999</v>
+        <v>51634.58</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>63712.79</v>
+        <v>58236.08</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>12.5</v>
+        <v>-11.3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-15.3</v>
+        <v>-9.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>34.4</v>
+        <v>15.7</v>
       </c>
       <c r="H5" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -2845,60 +2937,60 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>21071.99</v>
+        <v>22431.31</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>26041.96</v>
+        <v>25316.62</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-19.1</v>
+        <v>-11.4</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-24.8</v>
+        <v>-9.6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
       <c r="B8" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>147541.46</v>
+        <v>124279.63</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>140124.23</v>
+        <v>133193.68</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5.3</v>
+        <v>-6.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>23</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>92390.67</v>
+        <v>87128.17</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>92792.05</v>
+        <v>89177.03999999999</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.4</v>
+        <v>-2.3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>18.2</v>
+        <v>11.9</v>
       </c>
     </row>
   </sheetData>
